--- a/engine/publish_queue/PHDC/PHDC_Valuation_Model_03092026.xlsx
+++ b/engine/publish_queue/PHDC/PHDC_Valuation_Model_03092026.xlsx
@@ -5103,19 +5103,19 @@
         </is>
       </c>
       <c r="B4" s="29" t="n">
-        <v>0.2110848413262307</v>
+        <v>0.2110196958005933</v>
       </c>
       <c r="C4" s="29" t="n">
-        <v>0.2310848413262307</v>
+        <v>0.2310196958005933</v>
       </c>
       <c r="D4" s="29" t="n">
-        <v>0.2510848413262307</v>
+        <v>0.2510196958005933</v>
       </c>
       <c r="E4" s="29" t="n">
-        <v>0.2710848413262307</v>
+        <v>0.2710196958005933</v>
       </c>
       <c r="F4" s="29" t="n">
-        <v>0.2910848413262307</v>
+        <v>0.2910196958005933</v>
       </c>
     </row>
     <row r="5">
@@ -5123,16 +5123,16 @@
         <v>0.03937593483976742</v>
       </c>
       <c r="B5" s="7" t="n">
-        <v>15.25</v>
+        <v>15.27</v>
       </c>
       <c r="C5" s="7" t="n">
-        <v>9.44</v>
+        <v>9.449999999999999</v>
       </c>
       <c r="D5" s="7" t="n">
-        <v>6.14</v>
+        <v>6.15</v>
       </c>
       <c r="E5" s="7" t="n">
-        <v>4.01</v>
+        <v>4.02</v>
       </c>
       <c r="F5" s="7" t="n">
         <v>2.52</v>
@@ -5143,13 +5143,13 @@
         <v>0.06</v>
       </c>
       <c r="B6" s="7" t="n">
-        <v>24.81</v>
+        <v>24.84</v>
       </c>
       <c r="C6" s="7" t="n">
-        <v>16.1</v>
+        <v>16.12</v>
       </c>
       <c r="D6" s="7" t="n">
-        <v>11.2</v>
+        <v>11.21</v>
       </c>
       <c r="E6" s="7" t="n">
         <v>8.050000000000001</v>
@@ -5163,19 +5163,19 @@
         <v>0.08713663734609707</v>
       </c>
       <c r="B7" s="7" t="n">
-        <v>37.4</v>
+        <v>37.44</v>
       </c>
       <c r="C7" s="7" t="n">
-        <v>24.88</v>
+        <v>24.9</v>
       </c>
       <c r="D7" s="7" t="n">
-        <v>17.85</v>
+        <v>17.86</v>
       </c>
       <c r="E7" s="7" t="n">
-        <v>13.36</v>
+        <v>13.37</v>
       </c>
       <c r="F7" s="7" t="n">
-        <v>10.24</v>
+        <v>10.25</v>
       </c>
     </row>
     <row r="8">
@@ -5183,19 +5183,19 @@
         <v>0.12</v>
       </c>
       <c r="B8" s="7" t="n">
-        <v>52.64</v>
+        <v>52.7</v>
       </c>
       <c r="C8" s="7" t="n">
-        <v>35.5</v>
+        <v>35.53</v>
       </c>
       <c r="D8" s="7" t="n">
-        <v>25.9</v>
+        <v>25.92</v>
       </c>
       <c r="E8" s="7" t="n">
-        <v>19.78</v>
+        <v>19.8</v>
       </c>
       <c r="F8" s="7" t="n">
-        <v>15.56</v>
+        <v>15.57</v>
       </c>
     </row>
     <row r="9">
@@ -5203,19 +5203,19 @@
         <v>0.1787001284632628</v>
       </c>
       <c r="B9" s="7" t="n">
-        <v>79.86</v>
+        <v>79.95</v>
       </c>
       <c r="C9" s="7" t="n">
-        <v>54.48</v>
+        <v>54.52</v>
       </c>
       <c r="D9" s="7" t="n">
-        <v>40.29</v>
+        <v>40.32</v>
       </c>
       <c r="E9" s="7" t="n">
-        <v>31.27</v>
+        <v>31.29</v>
       </c>
       <c r="F9" s="7" t="n">
-        <v>25.05</v>
+        <v>25.06</v>
       </c>
     </row>
   </sheetData>
@@ -5419,13 +5419,13 @@
         </is>
       </c>
       <c r="C5" s="31" t="n">
-        <v>1.4718</v>
+        <v>1.4687</v>
       </c>
       <c r="D5" s="26" t="n">
-        <v>0.3261</v>
+        <v>0.3252</v>
       </c>
       <c r="E5" s="32" t="n">
-        <v>0.1848</v>
+        <v>0.1833</v>
       </c>
       <c r="F5" s="26" t="n">
         <v>0.4394</v>
@@ -5446,13 +5446,13 @@
         </is>
       </c>
       <c r="C6" s="31" t="n">
-        <v>1.0493</v>
+        <v>1.0481</v>
       </c>
       <c r="D6" s="26" t="n">
-        <v>0.2988</v>
+        <v>0.2997</v>
       </c>
       <c r="E6" s="32" t="n">
-        <v>0.1823</v>
+        <v>0.1808</v>
       </c>
       <c r="F6" s="26" t="n">
         <v>0.4391</v>
@@ -5473,16 +5473,16 @@
         </is>
       </c>
       <c r="C7" s="31" t="n">
-        <v>0.8837</v>
+        <v>0.8817</v>
       </c>
       <c r="D7" s="26" t="n">
-        <v>0.321</v>
+        <v>0.3251</v>
       </c>
       <c r="E7" s="32" t="n">
-        <v>0.173</v>
+        <v>0.1727</v>
       </c>
       <c r="F7" s="26" t="n">
-        <v>0.4636</v>
+        <v>0.4619</v>
       </c>
       <c r="G7" s="26" t="n">
         <v>-0.4293</v>
@@ -5500,13 +5500,13 @@
         </is>
       </c>
       <c r="C8" s="31" t="n">
-        <v>0.7653</v>
+        <v>0.7648</v>
       </c>
       <c r="D8" s="26" t="n">
-        <v>0.2884</v>
+        <v>0.2874</v>
       </c>
       <c r="E8" s="32" t="n">
-        <v>0.1815</v>
+        <v>0.1803</v>
       </c>
       <c r="F8" s="26" t="n">
         <v>0.444</v>
@@ -5527,16 +5527,16 @@
         </is>
       </c>
       <c r="C9" s="31" t="n">
-        <v>0.7388</v>
+        <v>0.7349</v>
       </c>
       <c r="D9" s="26" t="n">
-        <v>0.2441</v>
+        <v>0.2423</v>
       </c>
       <c r="E9" s="32" t="n">
-        <v>0.1692</v>
+        <v>0.1693</v>
       </c>
       <c r="F9" s="26" t="n">
-        <v>0.4106</v>
+        <v>0.412</v>
       </c>
       <c r="G9" s="26" t="n">
         <v>-0.4712</v>
@@ -5554,13 +5554,13 @@
         </is>
       </c>
       <c r="C10" s="31" t="n">
-        <v>0.7067</v>
+        <v>0.7006</v>
       </c>
       <c r="D10" s="26" t="n">
-        <v>0.2576</v>
+        <v>0.2565</v>
       </c>
       <c r="E10" s="32" t="n">
-        <v>0.1864</v>
+        <v>0.1854</v>
       </c>
       <c r="F10" s="26" t="n">
         <v>0.4217</v>
@@ -5581,16 +5581,16 @@
         </is>
       </c>
       <c r="C11" s="31" t="n">
-        <v>0.4938</v>
+        <v>0.4949</v>
       </c>
       <c r="D11" s="26" t="n">
-        <v>0.1033</v>
+        <v>0.1018</v>
       </c>
       <c r="E11" s="32" t="n">
-        <v>0.2237</v>
+        <v>0.2275</v>
       </c>
       <c r="F11" s="26" t="n">
-        <v>0.4713</v>
+        <v>0.4755</v>
       </c>
       <c r="G11" s="26" t="n">
         <v>-0.4658</v>
@@ -5672,13 +5672,13 @@
         </is>
       </c>
       <c r="B5" s="7" t="n">
-        <v>4.01</v>
+        <v>4.02</v>
       </c>
       <c r="C5" s="7" t="n">
-        <v>17.85</v>
+        <v>17.86</v>
       </c>
       <c r="D5" s="7" t="n">
-        <v>46.5</v>
+        <v>46.53</v>
       </c>
       <c r="E5" s="7" t="n"/>
     </row>
@@ -5723,13 +5723,13 @@
         </is>
       </c>
       <c r="B8" s="7" t="n">
-        <v>4.01</v>
+        <v>4.02</v>
       </c>
       <c r="C8" s="7" t="n">
-        <v>17.85</v>
+        <v>17.86</v>
       </c>
       <c r="D8" s="7" t="n">
-        <v>46.5</v>
+        <v>46.53</v>
       </c>
       <c r="E8" s="7" t="n">
         <v>1</v>
@@ -5764,13 +5764,13 @@
         </is>
       </c>
       <c r="B11" s="7" t="n">
-        <v>6.14</v>
+        <v>6.15</v>
       </c>
       <c r="C11" s="7" t="n">
-        <v>17565</v>
+        <v>17584</v>
       </c>
       <c r="D11" s="7" t="n">
-        <v>36814</v>
+        <v>36833</v>
       </c>
     </row>
     <row r="12">
@@ -5780,13 +5780,13 @@
         </is>
       </c>
       <c r="B12" s="7" t="n">
-        <v>17.85</v>
+        <v>17.86</v>
       </c>
       <c r="C12" s="7" t="n">
-        <v>51043</v>
+        <v>51083</v>
       </c>
       <c r="D12" s="7" t="n">
-        <v>71937</v>
+        <v>71979</v>
       </c>
     </row>
     <row r="13">
@@ -5796,13 +5796,13 @@
         </is>
       </c>
       <c r="B13" s="7" t="n">
-        <v>40.29</v>
+        <v>40.32</v>
       </c>
       <c r="C13" s="7" t="n">
-        <v>115225</v>
+        <v>115306</v>
       </c>
       <c r="D13" s="7" t="n">
-        <v>139273</v>
+        <v>139357</v>
       </c>
     </row>
     <row r="14">
@@ -5812,13 +5812,13 @@
         </is>
       </c>
       <c r="B14" s="7" t="n">
-        <v>17.46</v>
+        <v>17.47</v>
       </c>
       <c r="C14" s="7" t="n">
-        <v>49934</v>
+        <v>49977</v>
       </c>
       <c r="D14" s="7" t="n">
-        <v>70773</v>
+        <v>70818</v>
       </c>
     </row>
     <row r="16">
@@ -5848,7 +5848,7 @@
         </is>
       </c>
       <c r="B18" s="9" t="n">
-        <v>0.0731</v>
+        <v>0.073</v>
       </c>
     </row>
     <row r="20">
@@ -5865,7 +5865,7 @@
         </is>
       </c>
       <c r="B21" s="9" t="n">
-        <v>0.2609671471091543</v>
+        <v>0.2608706403474768</v>
       </c>
     </row>
     <row r="22">
@@ -5875,7 +5875,7 @@
         </is>
       </c>
       <c r="B22" s="9" t="n">
-        <v>0.2510848413262307</v>
+        <v>0.2510196958005933</v>
       </c>
     </row>
     <row r="23">
@@ -5927,7 +5927,7 @@
         </is>
       </c>
       <c r="B4" s="10" t="n">
-        <v>49462.4</v>
+        <v>49477.7</v>
       </c>
     </row>
     <row r="5">
@@ -5937,7 +5937,7 @@
         </is>
       </c>
       <c r="B5" s="10" t="n">
-        <v>22474.6</v>
+        <v>22501.1</v>
       </c>
     </row>
     <row r="6">
@@ -6212,7 +6212,7 @@
         </is>
       </c>
       <c r="B12" s="12" t="n">
-        <v>0.2609671471091543</v>
+        <v>0.2608706403474768</v>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
@@ -6503,7 +6503,7 @@
         </is>
       </c>
       <c r="B4" s="10" t="n">
-        <v>71936.89999999999</v>
+        <v>71978.8</v>
       </c>
     </row>
     <row r="5">
@@ -8009,49 +8009,49 @@
         </is>
       </c>
       <c r="B16" s="12" t="n">
-        <v>0.251085</v>
+        <v>0.25102</v>
       </c>
       <c r="C16" s="12" t="n">
-        <v>0.219107</v>
+        <v>0.219048</v>
       </c>
       <c r="D16" s="12" t="n">
-        <v>0.193525</v>
+        <v>0.19347</v>
       </c>
       <c r="E16" s="12" t="n">
-        <v>0.174338</v>
+        <v>0.174287</v>
       </c>
       <c r="F16" s="12" t="n">
-        <v>0.161547</v>
+        <v>0.161499</v>
       </c>
       <c r="G16" s="12" t="n">
-        <v>0.161547</v>
+        <v>0.161499</v>
       </c>
       <c r="H16" s="12" t="n">
-        <v>0.161547</v>
+        <v>0.161499</v>
       </c>
       <c r="I16" s="12" t="n">
-        <v>0.161547</v>
+        <v>0.161499</v>
       </c>
       <c r="J16" s="12" t="n">
-        <v>0.161547</v>
+        <v>0.161499</v>
       </c>
       <c r="K16" s="12" t="n">
-        <v>0.161547</v>
+        <v>0.161499</v>
       </c>
       <c r="L16" s="12" t="n">
-        <v>0.161547</v>
+        <v>0.161499</v>
       </c>
       <c r="M16" s="12" t="n">
-        <v>0.161547</v>
+        <v>0.161499</v>
       </c>
       <c r="N16" s="12" t="n">
-        <v>0.161547</v>
+        <v>0.161499</v>
       </c>
       <c r="O16" s="12" t="n">
-        <v>0.161547</v>
+        <v>0.161499</v>
       </c>
       <c r="P16" s="12" t="n">
-        <v>0.161547</v>
+        <v>0.161499</v>
       </c>
     </row>
     <row r="17">
@@ -8206,7 +8206,7 @@
         </is>
       </c>
       <c r="B21" s="24" t="n">
-        <v>22474.6</v>
+        <v>22501.1</v>
       </c>
     </row>
     <row r="22">
